--- a/data/location.xlsx
+++ b/data/location.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\tickin-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BB6DBB-176A-45D6-98CF-9CC793C09B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7784EA-C439-443B-B5BE-0A92490F33CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
   <si>
     <t>LOCATION</t>
   </si>
@@ -395,13 +395,16 @@
   </si>
   <si>
     <t>Distributor_Code</t>
+  </si>
+  <si>
+    <t>SASTHA AGENCY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,6 +428,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -520,7 +530,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -537,6 +547,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -840,10 +851,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="38.85546875" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="139.140625" customWidth="1"/>
@@ -870,7 +881,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -884,7 +895,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -898,7 +909,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -1192,7 +1203,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="14" t="s">
         <v>73</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1289,6 +1300,11 @@
       </c>
       <c r="B32" s="11" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
